--- a/GRAMMAR/11_17_07.xlsx
+++ b/GRAMMAR/11_17_07.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\GRAMMAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED912FCE-A0AD-48B4-9FDA-2C3C259B1404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17355637-2866-494A-B7D3-F4C15C20B670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10560" yWindow="915" windowWidth="27840" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1560" windowWidth="27840" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/GRAMMAR/11_17_07.xlsx
+++ b/GRAMMAR/11_17_07.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\GRAMMAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17355637-2866-494A-B7D3-F4C15C20B670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B9852D-7F58-47CA-913A-643A68DE9D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1560" windowWidth="27840" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19140" yWindow="1005" windowWidth="19260" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>Fre</t>
   </si>
@@ -131,10 +131,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>〜てはならない：禁止</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>てもしかたない</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -148,10 +144,6 @@
   </si>
   <si>
     <t>成长，发育</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>お～です</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -226,12 +218,164 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t>お～です/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>でしたら</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>お～する 自谦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かのように</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好像…一样</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>というように -&gt;列举</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>というように</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>列举</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かのように -&gt; 好像…一样</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜てはならない</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>てはならない：</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>禁止</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>よう＋とする</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正想要…(表示说话人做某事的意图)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>はずがない</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可能…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>いくつになっても</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>无论多少岁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力が落ちる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力下降</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>マスターズ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Masters，大师赛，硕士学位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>にとどまらない</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不只限于……范围，涉及得更广</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ともに</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一起；同时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>のか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不确定语气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,6 +414,28 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -306,12 +472,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -616,7 +788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
@@ -718,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>18</v>
@@ -760,7 +932,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>0</v>
       </c>
@@ -770,8 +942,8 @@
       <c r="C12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>28</v>
+      <c r="E12" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
@@ -779,10 +951,10 @@
         <v>0</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.15">
@@ -790,21 +962,24 @@
         <v>0</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="2" t="s">
+    </row>
+    <row r="15" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A15" s="2">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A15" s="2">
-        <v>0</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>34</v>
+      <c r="E15" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
@@ -812,54 +987,181 @@
         <v>0</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A17" s="2">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A17" s="2">
-        <v>0</v>
-      </c>
-      <c r="B17" s="2" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A18" s="2">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A18" s="2">
-        <v>0</v>
-      </c>
-      <c r="B18" s="2" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19" s="2">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A19" s="2">
-        <v>0</v>
-      </c>
-      <c r="B19" s="2" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A20" s="2">
+        <v>0</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A20" s="2">
-        <v>0</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>44</v>
+    <row r="21" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A21" s="2">
+        <v>0</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A22" s="2">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A23" s="2">
+        <v>0</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A24" s="2">
+        <v>0</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A25" s="2">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A26" s="2">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A27" s="2">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A28" s="2">
+        <v>0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A29" s="2">
+        <v>0</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A30" s="2">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A31" s="2">
+        <v>0</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
